--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104714_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104714_W29.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.3433</v>
+        <v>11.9658</v>
       </c>
       <c r="E2" t="n">
-        <v>9.489100000000001</v>
+        <v>10.2485</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8542</v>
+        <v>1.7174</v>
       </c>
       <c r="G2" t="n">
-        <v>7.6306</v>
+        <v>7.6277</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2322</v>
+        <v>1.2345</v>
       </c>
       <c r="I2" t="n">
-        <v>6.3984</v>
+        <v>6.3931</v>
       </c>
       <c r="J2" t="n">
-        <v>7.8429</v>
+        <v>7.8283</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8033</v>
+        <v>1.7959</v>
       </c>
       <c r="L2" t="n">
-        <v>6.0396</v>
+        <v>6.0324</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2123</v>
+        <v>-0.2006</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.5613</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3588</v>
+        <v>0.3608</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2873</v>
+        <v>0.3382</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5363</v>
+        <v>0.2413</v>
       </c>
       <c r="U2" t="n">
-        <v>0.249</v>
+        <v>0.0969</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0514</v>
+        <v>6.5652</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8309</v>
+        <v>5.3584</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2205</v>
+        <v>1.2068</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6937</v>
+        <v>4.6928</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0661</v>
+        <v>1.0706</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6276</v>
+        <v>3.6223</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0487</v>
+        <v>5.0369</v>
       </c>
       <c r="K3" t="n">
-        <v>1.78</v>
+        <v>1.7754</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2688</v>
+        <v>3.2615</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.355</v>
+        <v>-0.3441</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7139</v>
+        <v>-0.7048</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3588</v>
+        <v>0.3608</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7783</v>
+        <v>-0.2658</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7635</v>
+        <v>-0.2232</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0148</v>
+        <v>-0.0425</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6091</v>
+        <v>5.016</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3953</v>
+        <v>3.256</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2138</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5114</v>
+        <v>3.5048</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4216</v>
+        <v>2.416</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0898</v>
+        <v>1.0888</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2757</v>
+        <v>3.2608</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7598</v>
+        <v>2.7472</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5159</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2357</v>
+        <v>0.244</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3382</v>
+        <v>-0.3312</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5739</v>
+        <v>0.5752</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>0.552</v>
+        <v>-0.0335</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1642</v>
+        <v>0.0439</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3878</v>
+        <v>-0.0774</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8424</v>
+        <v>3.863</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8789</v>
+        <v>1.5715</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9636</v>
+        <v>2.2916</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5153</v>
+        <v>1.5202</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7896</v>
+        <v>0.7948</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7257</v>
+        <v>0.7255</v>
       </c>
       <c r="J5" t="n">
-        <v>0.979</v>
+        <v>0.9748</v>
       </c>
       <c r="K5" t="n">
-        <v>0.985</v>
+        <v>0.9825</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.006</v>
+        <v>-0.0077</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5362</v>
+        <v>0.5454</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1954</v>
+        <v>-0.1877</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7317</v>
+        <v>0.7331</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3506</v>
+        <v>0.3624</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8998</v>
+        <v>0.5966</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5492</v>
+        <v>-0.2342</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2019</v>
+        <v>2.2114</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5962</v>
+        <v>0.2063</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7981</v>
+        <v>2.0051</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.018</v>
+        <v>-1.0251</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.819</v>
+        <v>-0.8185</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1991</v>
+        <v>-0.2066</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1965</v>
+        <v>-1.2126</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.6452</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5579</v>
+        <v>-0.5673</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1785</v>
+        <v>0.1875</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1804</v>
+        <v>-0.1733</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3588</v>
+        <v>0.3608</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3484</v>
+        <v>0.669</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6057</v>
+        <v>0.2203</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2573</v>
+        <v>0.4487</v>
       </c>
       <c r="V6" t="n">
-        <v>2.7955</v>
+        <v>2.7951</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3419</v>
+        <v>2.3367</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4536</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0862</v>
+        <v>1.7577</v>
       </c>
       <c r="E7" t="n">
-        <v>2.331</v>
+        <v>2.8573</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2449</v>
+        <v>-1.0996</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6665</v>
+        <v>2.0495</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3223</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3442</v>
+        <v>2.929</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2143</v>
+        <v>4.6161</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9528</v>
+        <v>0.9308</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2616</v>
+        <v>3.6853</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5479</v>
+        <v>-2.5667</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6305</v>
+        <v>-1.8103</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9174</v>
+        <v>-0.7563</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4544</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.874</v>
+        <v>0.6886</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2526</v>
+        <v>0.3597</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6214</v>
+        <v>0.3289</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5128</v>
+        <v>1.0713</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5741000000000001</v>
+        <v>2.4579</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0869</v>
+        <v>-1.3866</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.377</v>
+        <v>0.6684</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6093</v>
+        <v>0.3242</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2323</v>
+        <v>0.3441</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6625</v>
+        <v>3.2061</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7371</v>
+        <v>1.9478</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0746</v>
+        <v>1.2584</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2855</v>
+        <v>-2.5378</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1277</v>
+        <v>-1.6235</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1578</v>
+        <v>-0.9143</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4544</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4354</v>
+        <v>0.8582</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.3899</v>
       </c>
       <c r="U8" t="n">
-        <v>0.347</v>
+        <v>0.4683</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4541</v>
+        <v>0.8709</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9132</v>
+        <v>-0.2199</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4591</v>
+        <v>1.0908</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0534</v>
+        <v>-0.3765</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8851</v>
+        <v>-0.6089</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9385</v>
+        <v>0.2324</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6313</v>
+        <v>-0.6635</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9332</v>
+        <v>-0.7379</v>
       </c>
       <c r="L9" t="n">
-        <v>3.6981</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5779</v>
+        <v>0.287</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8183</v>
+        <v>0.129</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7596000000000001</v>
+        <v>0.1579</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1359</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1359</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6228</v>
+        <v>0.7921</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6057</v>
+        <v>0.4436</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0171</v>
+        <v>0.3485</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1594</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1594</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3948</v>
+        <v>0.6365</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6669</v>
+        <v>2.1241</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.272</v>
+        <v>-1.4875</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5442</v>
+        <v>-0.2087</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8198</v>
+        <v>-1.0459</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2756</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8726</v>
+        <v>1.6553</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6927</v>
+        <v>0.4342</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8202</v>
+        <v>1.2211</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6716</v>
+        <v>-1.864</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1271</v>
+        <v>-1.48</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5446</v>
+        <v>-0.384</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1359</v>
+        <v>1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1359</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>5.5524</v>
+        <v>0.1835</v>
       </c>
       <c r="T10" t="n">
-        <v>4.4243</v>
+        <v>0.311</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1281</v>
+        <v>-0.1275</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4775</v>
+        <v>-0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.613</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.268</v>
+        <v>-0.2352</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5903</v>
+        <v>0.5888</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8583</v>
+        <v>-0.824</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5752</v>
+        <v>0.5744</v>
       </c>
       <c r="H11" t="n">
-        <v>0.538</v>
+        <v>0.5371</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5903</v>
+        <v>0.5888</v>
       </c>
       <c r="K11" t="n">
-        <v>0.553</v>
+        <v>0.5516</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.015</v>
+        <v>-0.0144</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.015</v>
+        <v>-0.0144</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0208</v>
+        <v>0.0523</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0208</v>
+        <v>0.0523</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4069</v>
+        <v>-0.3163</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2855</v>
+        <v>1.0408</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6924</v>
+        <v>-1.3571</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2122</v>
+        <v>-0.3884</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0497</v>
+        <v>-0.6401</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8375</v>
+        <v>0.2517</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6624</v>
+        <v>1.7192</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4381</v>
+        <v>0.6098</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2243</v>
+        <v>1.1094</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8745</v>
+        <v>-2.1077</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4877</v>
+        <v>-1.2499</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3868</v>
+        <v>-0.8578</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5903</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5903</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8532</v>
+        <v>0.5062</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5363</v>
+        <v>0.5084</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3169</v>
+        <v>-0.0022</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9318</v>
+        <v>0.9317</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1594</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0913</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6854</v>
+        <v>-2.5697</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8708</v>
+        <v>-1.8797</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5562</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3856</v>
+        <v>-2.5402</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6379</v>
+        <v>-2.8175</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2523</v>
+        <v>0.2773</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7294</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6169</v>
+        <v>-1.6967</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1124</v>
+        <v>0.8192</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1149</v>
+        <v>-1.6628</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2548</v>
+        <v>-1.1209</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8601</v>
+        <v>-0.5419</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3631</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9087</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1314</v>
+        <v>2.5851</v>
       </c>
       <c r="T13" t="n">
-        <v>0.322</v>
+        <v>1.8903</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1906</v>
+        <v>0.6948</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9318</v>
+        <v>-1.4764</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0913</v>
+        <v>-0.6162</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1594</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>30.1357</v>
+        <v>30.83659999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>27.0816</v>
+        <v>27.61</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0542</v>
+        <v>3.2269</v>
       </c>
       <c r="G14" t="n">
-        <v>16.1091</v>
+        <v>16.0989</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4509999999999988</v>
+        <v>-0.4331999999999994</v>
       </c>
       <c r="I14" t="n">
-        <v>16.5601</v>
+        <v>16.532</v>
       </c>
       <c r="J14" t="n">
-        <v>26.2424</v>
+        <v>26.1327</v>
       </c>
       <c r="K14" t="n">
-        <v>8.753699999999998</v>
+        <v>8.695400000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>17.4889</v>
+        <v>17.4376</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.1332</v>
+        <v>-10.0342</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.204700000000001</v>
+        <v>-9.128300000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9286999999999999</v>
+        <v>-0.9056999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>3.407900000000001</v>
+        <v>3.414399999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2234</v>
+        <v>-10.2435</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6311</v>
+        <v>13.6579</v>
       </c>
       <c r="S14" t="n">
-        <v>6.0266</v>
+        <v>6.7363</v>
       </c>
       <c r="T14" t="n">
-        <v>4.1038</v>
+        <v>4.7818</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9228</v>
+        <v>1.9546</v>
       </c>
       <c r="V14" t="n">
-        <v>4.591700000000001</v>
+        <v>4.5871</v>
       </c>
       <c r="W14" t="n">
-        <v>6.958399999999999</v>
+        <v>6.938700000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.3666</v>
+        <v>-2.3517</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2765</v>
+        <v>1.6607</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1415</v>
+        <v>2.6041</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8649</v>
+        <v>-0.9434</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5871</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4652</v>
+        <v>2.4616</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.878</v>
+        <v>-1.8734</v>
       </c>
       <c r="J15" t="n">
-        <v>2.886</v>
+        <v>2.8786</v>
       </c>
       <c r="K15" t="n">
-        <v>2.886</v>
+        <v>2.8786</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2988</v>
+        <v>-2.2904</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4208</v>
+        <v>-0.4169</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.878</v>
+        <v>-1.8734</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0596</v>
+        <v>-0.6818</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.2744</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3151</v>
+        <v>-0.4074</v>
       </c>
       <c r="V15" t="n">
-        <v>0.613</v>
+        <v>0.6162</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.613</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.439</v>
+        <v>1.108</v>
       </c>
       <c r="E16" t="n">
-        <v>2.979</v>
+        <v>3.437</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.54</v>
+        <v>-2.329</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7392</v>
+        <v>-0.734</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6387</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1005</v>
+        <v>-0.1014</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7711</v>
+        <v>2.7613</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0369</v>
+        <v>1.0342</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7342</v>
+        <v>1.7271</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.5103</v>
+        <v>-3.4954</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6756</v>
+        <v>-1.6668</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8348</v>
+        <v>-1.8285</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0489</v>
+        <v>-0.3856</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8833</v>
+        <v>-0.4138</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1656</v>
+        <v>0.0283</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1919</v>
+        <v>-0.8879</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1983</v>
+        <v>2.3631</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.3902</v>
+        <v>-3.251</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3189</v>
+        <v>-0.3172</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6071</v>
+        <v>0.6061</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.926</v>
+        <v>-0.9233</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8081</v>
+        <v>1.8037</v>
       </c>
       <c r="K17" t="n">
-        <v>1.659</v>
+        <v>1.6547</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1491</v>
+        <v>0.1489</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1271</v>
+        <v>-2.1209</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0519</v>
+        <v>-1.0487</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0752</v>
+        <v>-1.0722</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4686</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2308</v>
+        <v>0.4016</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2378</v>
+        <v>0.3659</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.0231</v>
+        <v>-2.0212</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4673</v>
+        <v>-0.8908</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4109</v>
+        <v>1.0333</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8783</v>
+        <v>-1.9241</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3294</v>
+        <v>1.3257</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4818</v>
+        <v>2.4737</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1524</v>
+        <v>-1.148</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7971</v>
+        <v>2.7844</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7598</v>
+        <v>2.7472</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4677</v>
+        <v>-1.4587</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.278</v>
+        <v>-0.2734</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1897</v>
+        <v>-1.1852</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6381</v>
+        <v>-1.0557</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1828</v>
+        <v>-0.5415</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4553</v>
+        <v>-0.5141</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1587</v>
+        <v>-1.1609</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0674</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6448</v>
+        <v>-1.3187</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0372</v>
+        <v>-0.7542</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6075</v>
+        <v>-0.5645</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9411</v>
+        <v>-1.9383</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6575</v>
+        <v>-1.6571</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2836</v>
+        <v>-0.2812</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2873</v>
+        <v>-0.2913</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9211</v>
+        <v>-0.9243</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6338</v>
+        <v>0.633</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6537</v>
+        <v>-1.6471</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7363</v>
+        <v>-0.7328</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9174</v>
+        <v>-0.9143</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>1.16</v>
+        <v>0.483</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0225</v>
+        <v>0.311</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1374</v>
+        <v>0.1721</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7368</v>
+        <v>-2.9421</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7493</v>
+        <v>0.5003</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4861</v>
+        <v>-3.4423</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9066</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1023</v>
+        <v>2.0996</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1957</v>
+        <v>-1.1929</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5603</v>
+        <v>2.5538</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5231</v>
+        <v>2.5166</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6537</v>
+        <v>-1.6471</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4208</v>
+        <v>-0.4169</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2329</v>
+        <v>-1.2301</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0447</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1976</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4608</v>
+        <v>0.2228</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2633</v>
+        <v>-0.2309</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7963</v>
+        <v>-1.792</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7963</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1948</v>
+        <v>-3.0909</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.181</v>
+        <v>-1.3128</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0138</v>
+        <v>-1.7781</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.73</v>
+        <v>-2.7287</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2713</v>
+        <v>-2.2716</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4587</v>
+        <v>-0.4571</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1399</v>
+        <v>-0.1488</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6559</v>
+        <v>-0.6625</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5159</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5901</v>
+        <v>-2.5799</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6154</v>
+        <v>-1.6091</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9746</v>
+        <v>-0.9708</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.0232</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0948</v>
+        <v>-0.0258</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.173</v>
+        <v>0.049</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3621</v>
+        <v>-3.3779</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2176</v>
+        <v>-0.0136</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1445</v>
+        <v>-3.3643</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.595</v>
+        <v>-1.3202</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3914</v>
+        <v>-1.0659</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.2035</v>
+        <v>-0.2543</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8568</v>
+        <v>1.703</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3163</v>
+        <v>0.3997</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5405</v>
+        <v>1.3033</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7382</v>
+        <v>-3.0232</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0752</v>
+        <v>-1.4656</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.663</v>
+        <v>-1.5576</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9087</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2897</v>
+        <v>-0.4855</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0254</v>
+        <v>-0.4811</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3151</v>
+        <v>-0.0044</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3862</v>
+        <v>0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3862</v>
+        <v>2.1789</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1739</v>
+        <v>-3.5736</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3498</v>
+        <v>-2.3456</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.824</v>
+        <v>-1.2281</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3268</v>
+        <v>-3.5943</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0692</v>
+        <v>-0.3932</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2576</v>
+        <v>-3.2011</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7083</v>
+        <v>-1.863</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4035</v>
+        <v>-0.321</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3048</v>
+        <v>-1.542</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.0352</v>
+        <v>-1.7312</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4727</v>
+        <v>-0.0722</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5625</v>
+        <v>-1.659</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.4991</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4078</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2798</v>
+        <v>-0.5029</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8329</v>
+        <v>-0.0955</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.447</v>
+        <v>-0.4074</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9318</v>
+        <v>-0.387</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1825</v>
+        <v>-0.387</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8605</v>
+        <v>-4.4992</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0298</v>
+        <v>-2.9324</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8307</v>
+        <v>-1.5668</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6366</v>
+        <v>-1.6387</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1367</v>
+        <v>-0.1402</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4999</v>
+        <v>-1.4985</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1539</v>
+        <v>-0.1656</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1564</v>
+        <v>0.1477</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3102</v>
+        <v>-0.3132</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4827</v>
+        <v>-1.4731</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2931</v>
+        <v>-0.2879</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1897</v>
+        <v>-1.1852</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.793</v>
+        <v>-1.4249</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7635</v>
+        <v>-0.6483</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0295</v>
+        <v>-0.7766</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. WALKER</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.0391</v>
+        <v>-5.366</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9238</v>
+        <v>-3.3404</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1152</v>
+        <v>-2.0257</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4538</v>
+        <v>-4.193</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5838</v>
+        <v>-0.4617</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.8701</v>
+        <v>-3.7314</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2545</v>
+        <v>-1.7187</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1676</v>
+        <v>-0.5041</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4221</v>
+        <v>-1.2146</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.1994</v>
+        <v>-2.4744</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7514</v>
+        <v>0.0424</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.448</v>
+        <v>-2.5168</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8175</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4544</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6765</v>
+        <v>-1.173</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3975</v>
+        <v>-0.4835</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.279</v>
+        <v>-0.6895</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>J. WALKER</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.1801</v>
+        <v>-5.382</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.794</v>
+        <v>-2.4655</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3861</v>
+        <v>-2.9164</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.1909</v>
+        <v>-2.4551</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4568</v>
+        <v>-0.5856</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.7341</v>
+        <v>-1.8695</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.7053</v>
+        <v>-0.2633</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4943</v>
+        <v>0.1616</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.211</v>
+        <v>-0.4249</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.4856</v>
+        <v>-2.1918</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0375</v>
+        <v>-0.7472</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.5231</v>
+        <v>-1.4446</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1359</v>
+        <v>0.4553</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.9892</v>
+        <v>-0.0163</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9527</v>
+        <v>0.0741</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0364</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-30.1358</v>
+        <v>-28.56039999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.054199999999999</v>
+        <v>-3.2267</v>
       </c>
       <c r="F27" t="n">
-        <v>-27.0813</v>
+        <v>-25.3337</v>
       </c>
       <c r="G27" t="n">
-        <v>-16.1092</v>
+        <v>-16.0988</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4509999999999998</v>
+        <v>0.4330999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-16.5601</v>
+        <v>-16.5321</v>
       </c>
       <c r="J27" t="n">
-        <v>10.1332</v>
+        <v>10.0341</v>
       </c>
       <c r="K27" t="n">
-        <v>9.204699999999997</v>
+        <v>9.128399999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>0.9286000000000001</v>
+        <v>0.9055999999999997</v>
       </c>
       <c r="M27" t="n">
-        <v>-26.2425</v>
+        <v>-26.1332</v>
       </c>
       <c r="N27" t="n">
-        <v>-8.7537</v>
+        <v>-8.6951</v>
       </c>
       <c r="O27" t="n">
-        <v>-17.4889</v>
+        <v>-17.4377</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.408</v>
+        <v>-3.4144</v>
       </c>
       <c r="Q27" t="n">
-        <v>-13.6312</v>
+        <v>-13.658</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2232</v>
+        <v>10.2435</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.026800000000001</v>
+        <v>-4.460100000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.9229</v>
+        <v>-1.9544</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.1041</v>
+        <v>-2.5054</v>
       </c>
       <c r="V27" t="n">
-        <v>-4.591899999999999</v>
+        <v>-4.5871</v>
       </c>
       <c r="W27" t="n">
-        <v>2.3666</v>
+        <v>2.3517</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.958500000000001</v>
+        <v>-6.9387</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104714_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104714_W29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-2.3517</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104714_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.9387</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
